--- a/docs/lem/files/xslope_reinforce.xlsx
+++ b/docs/lem/files/xslope_reinforce.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t>X</t>
   </si>
@@ -627,6 +627,37 @@
   </si>
   <si>
     <t>base</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8054,7 +8085,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9588,8 +9619,8 @@
       <c r="I8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="26" t="s">
-        <v>81</v>
+      <c r="J8" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="K8" s="21" t="s">
         <v>88</v>
@@ -9610,7 +9641,7 @@
         <v>82</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="R8" s="25" t="s">
         <v>92</v>
@@ -10360,7 +10391,7 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:F50">
+  <conditionalFormatting sqref="F9:F50">
     <cfRule type="expression" dxfId="8" priority="3">
       <formula>$D9="cp"</formula>
     </cfRule>
@@ -10375,7 +10406,7 @@
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N50">
+  <conditionalFormatting sqref="N9:N50">
     <cfRule type="expression" dxfId="5" priority="6">
       <formula>$D9="cp"</formula>
     </cfRule>

--- a/docs/lem/files/xslope_reinforce.xlsx
+++ b/docs/lem/files/xslope_reinforce.xlsx
@@ -1907,13 +1907,13 @@
           <t>Geosynthetic</t>
         </is>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="3" t="str">
         <f>IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="I3" s="3">
+        <v>Tangent</v>
+      </c>
+      <c r="I3" s="3" t="str">
         <f>IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J3" s="3" t="n">
         <v>800</v>
@@ -1980,13 +1980,13 @@
           <t>Geosynthetic</t>
         </is>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="3" t="str">
         <f>IF($G4="","",IFERROR(VLOOKUP($G4,$Z$8:$AB$11,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="I4" s="3">
+        <v>Tangent</v>
+      </c>
+      <c r="I4" s="3" t="str">
         <f>IF($G4="","",IFERROR(VLOOKUP($G4,$Z$8:$AB$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>800</v>
@@ -2043,13 +2043,13 @@
           <t>Geosynthetic</t>
         </is>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="3" t="str">
         <f>IF($G5="","",IFERROR(VLOOKUP($G5,$Z$8:$AB$11,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="I5" s="3">
+        <v>Tangent</v>
+      </c>
+      <c r="I5" s="3" t="str">
         <f>IF($G5="","",IFERROR(VLOOKUP($G5,$Z$8:$AB$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>800</v>
@@ -2106,13 +2106,13 @@
           <t>Geosynthetic</t>
         </is>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="3" t="str">
         <f>IF($G6="","",IFERROR(VLOOKUP($G6,$Z$8:$AB$11,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="I6" s="3">
+        <v>Tangent</v>
+      </c>
+      <c r="I6" s="3" t="str">
         <f>IF($G6="","",IFERROR(VLOOKUP($G6,$Z$8:$AB$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>800</v>
@@ -2164,13 +2164,13 @@
           <t>Geosynthetic</t>
         </is>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="3" t="str">
         <f>IF($G7="","",IFERROR(VLOOKUP($G7,$Z$8:$AB$11,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="I7" s="3">
+        <v>Tangent</v>
+      </c>
+      <c r="I7" s="3" t="str">
         <f>IF($G7="","",IFERROR(VLOOKUP($G7,$Z$8:$AB$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>800</v>
@@ -2222,13 +2222,13 @@
           <t>Geosynthetic</t>
         </is>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="str">
         <f>IF($G8="","",IFERROR(VLOOKUP($G8,$Z$8:$AB$11,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="I8" s="3">
+        <v>Tangent</v>
+      </c>
+      <c r="I8" s="3" t="str">
         <f>IF($G8="","",IFERROR(VLOOKUP($G8,$Z$8:$AB$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>800</v>

--- a/docs/lem/files/xslope_reinforce.xlsx
+++ b/docs/lem/files/xslope_reinforce.xlsx
@@ -1933,9 +1933,7 @@
       <c r="O3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="P3" s="3"/>
       <c r="Q3" s="3" t="n"/>
       <c r="R3" s="3" t="n"/>
       <c r="Z3" t="inlineStr">
@@ -2006,9 +2004,7 @@
       <c r="O4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" s="3"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
       <c r="Z4" t="inlineStr">
@@ -2069,9 +2065,7 @@
       <c r="O5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="P5" s="3"/>
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
       <c r="Z5" t="inlineStr">
@@ -2132,9 +2126,7 @@
       <c r="O6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="P6" s="3"/>
       <c r="Q6" s="3" t="n"/>
       <c r="R6" s="3" t="n"/>
     </row>
@@ -2190,9 +2182,7 @@
       <c r="O7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P7" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="P7" s="3"/>
       <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="n"/>
     </row>
@@ -2248,9 +2238,7 @@
       <c r="O8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P8" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="P8" s="3"/>
       <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="n"/>
       <c r="Z8" t="inlineStr">

--- a/docs/lem/files/xslope_reinforce.xlsx
+++ b/docs/lem/files/xslope_reinforce.xlsx
@@ -5503,7 +5503,23 @@
       </c>
       <c r="D10" s="48" t="inlineStr">
         <is>
-          <t>gsat</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>sat</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="44" t="inlineStr">

--- a/docs/lem/files/xslope_reinforce.xlsx
+++ b/docs/lem/files/xslope_reinforce.xlsx
@@ -2793,7 +2793,26 @@
       </c>
       <c r="H2" s="40" t="inlineStr">
         <is>
-          <t>qp</t>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>q</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>p</t>
+          </r>
         </is>
       </c>
       <c r="I2" s="40" t="inlineStr">
@@ -5634,12 +5653,64 @@
       </c>
       <c r="AA10" s="46" t="inlineStr">
         <is>
-          <t>s(g)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AB10" s="46" t="inlineStr">
         <is>
-          <t>s(c)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c)</t>
+          </r>
         </is>
       </c>
       <c r="AC10" s="47" t="inlineStr">
@@ -5649,17 +5720,70 @@
       </c>
       <c r="AD10" s="46" t="inlineStr">
         <is>
-          <t>s(c/p)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c/p)</t>
+          </r>
         </is>
       </c>
       <c r="AE10" s="46" t="inlineStr">
         <is>
-          <t>s(d)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(d)</t>
+          </r>
         </is>
       </c>
       <c r="AF10" s="47" t="inlineStr">
         <is>
-          <t>s(psi)</t>
+          <r>
+            <t>s(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>psi</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AG10" s="23" t="inlineStr">

--- a/docs/lem/files/xslope_reinforce.xlsx
+++ b/docs/lem/files/xslope_reinforce.xlsx
@@ -7709,14 +7709,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="56">
+      <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>shell</v>
       </c>
       <c r="B6" s="57" t="n"/>
-      <c r="D6" s="56">
+      <c r="D6" s="56" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>base</v>
       </c>
       <c r="E6" s="57" t="n"/>
       <c r="G6" s="56">
@@ -9336,14 +9336,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58">
+      <c r="A7" s="58" t="str">
         <f>IF(OR(B5="",B5="material"),_xlfn.XLOOKUP(B6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>shell</v>
       </c>
       <c r="B7" s="57" t="n"/>
-      <c r="D7" s="58">
+      <c r="D7" s="58" t="str">
         <f>IF(OR(E5="",E5="material"),_xlfn.XLOOKUP(E6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>base</v>
       </c>
       <c r="E7" s="57" t="n"/>
       <c r="G7" s="58">

--- a/docs/lem/files/xslope_reinforce.xlsx
+++ b/docs/lem/files/xslope_reinforce.xlsx
@@ -3340,7 +3340,7 @@
         <v>4.0</v>
       </c>
       <c r="L3" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -3407,7 +3407,7 @@
         <v>4.0</v>
       </c>
       <c r="L4" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -3468,7 +3468,7 @@
         <v>4.0</v>
       </c>
       <c r="L5" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -3529,7 +3529,7 @@
         <v>4.0</v>
       </c>
       <c r="L6" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -3587,7 +3587,7 @@
         <v>4.0</v>
       </c>
       <c r="L7" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3645,7 +3645,7 @@
         <v>4.0</v>
       </c>
       <c r="L8" s="3">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>

--- a/docs/lem/files/xslope_reinforce.xlsx
+++ b/docs/lem/files/xslope_reinforce.xlsx
@@ -3340,7 +3340,7 @@
         <v>4.0</v>
       </c>
       <c r="L3" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -3407,7 +3407,7 @@
         <v>4.0</v>
       </c>
       <c r="L4" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -3468,7 +3468,7 @@
         <v>4.0</v>
       </c>
       <c r="L5" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -3529,7 +3529,7 @@
         <v>4.0</v>
       </c>
       <c r="L6" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -3587,7 +3587,7 @@
         <v>4.0</v>
       </c>
       <c r="L7" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3645,7 +3645,7 @@
         <v>4.0</v>
       </c>
       <c r="L8" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>

--- a/docs/lem/files/xslope_reinforce.xlsx
+++ b/docs/lem/files/xslope_reinforce.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D385E8-F13F-8F45-A02D-F28142715816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12967D2-A998-D342-B5ED-43CABE326A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="4320" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15680" yWindow="4780" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="319">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -343,9 +343,6 @@
     <t>vg</t>
   </si>
   <si>
-    <t>van Genuchten model (a, n)</t>
-  </si>
-  <si>
     <t>pow</t>
   </si>
   <si>
@@ -875,9 +872,6 @@
   </si>
   <si>
     <t>I</t>
-  </si>
-  <si>
-    <t>Fixity</t>
   </si>
   <si>
     <t>P</t>
@@ -1122,6 +1116,27 @@
   </si>
   <si>
     <t>Delta</t>
+  </si>
+  <si>
+    <t>1D element size:</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Pinned</t>
+  </si>
+  <si>
+    <t>Unrotated</t>
+  </si>
+  <si>
+    <t>van Genuchten model (a, n, l)</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -2128,16 +2143,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>308429</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:rowOff>126999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>145143</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>553358</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2152,8 +2167,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13398500" y="190499"/>
-          <a:ext cx="3156858" cy="2349501"/>
+          <a:off x="14205857" y="126999"/>
+          <a:ext cx="3156858" cy="2521858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2458,7 +2473,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Fixity</a:t>
+            <a:t>Head</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
@@ -2470,8 +2485,54 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed or free)</a:t>
+            <a:t> = Pile head fixity status</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile tip fixity status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -2823,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2999,7 +3060,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>312</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -3011,7 +3072,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>49</v>
@@ -3023,28 +3084,34 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>48</v>
+      </c>
       <c r="F22" s="1"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-      <c r="C24" s="14" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D24"/>
+      <c r="D25"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
@@ -3088,7 +3155,7 @@
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D58" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
@@ -3186,7 +3253,7 @@
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -3204,10 +3271,10 @@
     <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>$D$75:$D$79</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D25" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"circular,non-circular"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3230,73 +3297,73 @@
   <sheetData>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="M2" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="Q2" s="27" t="s">
+      <c r="R2" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="R2" s="28" t="s">
+      <c r="S2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="T2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="S2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="T2" s="28" t="s">
+      <c r="AB2" t="s">
         <v>257</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>258</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>259</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.2">
@@ -3330,7 +3397,7 @@
         <v>Tangent</v>
       </c>
       <c r="I3" s="3" t="str">
-        <f>IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v>Active</v>
       </c>
       <c r="J3" s="3">
@@ -3357,13 +3424,13 @@
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="AB3" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC3" t="s">
         <v>261</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>262</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
@@ -3397,7 +3464,7 @@
         <v>Tangent</v>
       </c>
       <c r="I4" s="3" t="str">
-        <f>IF($G4="","",IFERROR(VLOOKUP($G4,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v>Active</v>
       </c>
       <c r="J4" s="3">
@@ -3424,7 +3491,7 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="AB4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -3458,7 +3525,7 @@
         <v>Tangent</v>
       </c>
       <c r="I5" s="3" t="str">
-        <f>IF($G5="","",IFERROR(VLOOKUP($G5,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v>Active</v>
       </c>
       <c r="J5" s="3">
@@ -3485,7 +3552,7 @@
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="AB5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
@@ -3519,7 +3586,7 @@
         <v>Tangent</v>
       </c>
       <c r="I6" s="3" t="str">
-        <f>IF($G6="","",IFERROR(VLOOKUP($G6,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v>Active</v>
       </c>
       <c r="J6" s="3">
@@ -3577,7 +3644,7 @@
         <v>Tangent</v>
       </c>
       <c r="I7" s="3" t="str">
-        <f>IF($G7="","",IFERROR(VLOOKUP($G7,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v>Active</v>
       </c>
       <c r="J7" s="3">
@@ -3635,7 +3702,7 @@
         <v>Tangent</v>
       </c>
       <c r="I8" s="3" t="str">
-        <f>IF($G8="","",IFERROR(VLOOKUP($G8,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v>Active</v>
       </c>
       <c r="J8" s="3">
@@ -3662,13 +3729,13 @@
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="AB8" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC8" t="s">
         <v>258</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AD8" t="s">
         <v>259</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
@@ -3686,7 +3753,7 @@
         <v/>
       </c>
       <c r="I9" s="3" t="str">
-        <f>IF($G9="","",IFERROR(VLOOKUP($G9,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J9" s="3"/>
@@ -3701,13 +3768,13 @@
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="AB9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC9" t="s">
         <v>261</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>262</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
@@ -3725,7 +3792,7 @@
         <v/>
       </c>
       <c r="I10" s="3" t="str">
-        <f>IF($G10="","",IFERROR(VLOOKUP($G10,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J10" s="3"/>
@@ -3740,13 +3807,13 @@
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="AB10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AC10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AD10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
@@ -3764,7 +3831,7 @@
         <v/>
       </c>
       <c r="I11" s="3" t="str">
-        <f>IF($G11="","",IFERROR(VLOOKUP($G11,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J11" s="3"/>
@@ -3779,13 +3846,13 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="AB11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AC11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AD11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
@@ -3803,7 +3870,7 @@
         <v/>
       </c>
       <c r="I12" s="3" t="str">
-        <f>IF($G12="","",IFERROR(VLOOKUP($G12,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J12" s="3"/>
@@ -3833,7 +3900,7 @@
         <v/>
       </c>
       <c r="I13" s="3" t="str">
-        <f>IF($G13="","",IFERROR(VLOOKUP($G13,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J13" s="3"/>
@@ -3863,7 +3930,7 @@
         <v/>
       </c>
       <c r="I14" s="3" t="str">
-        <f>IF($G14="","",IFERROR(VLOOKUP($G14,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J14" s="3"/>
@@ -3893,7 +3960,7 @@
         <v/>
       </c>
       <c r="I15" s="3" t="str">
-        <f>IF($G15="","",IFERROR(VLOOKUP($G15,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J15" s="3"/>
@@ -3923,7 +3990,7 @@
         <v/>
       </c>
       <c r="I16" s="3" t="str">
-        <f>IF($G16="","",IFERROR(VLOOKUP($G16,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J16" s="3"/>
@@ -3953,7 +4020,7 @@
         <v/>
       </c>
       <c r="I17" s="3" t="str">
-        <f>IF($G17="","",IFERROR(VLOOKUP($G17,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J17" s="3"/>
@@ -3983,7 +4050,7 @@
         <v/>
       </c>
       <c r="I18" s="3" t="str">
-        <f>IF($G18="","",IFERROR(VLOOKUP($G18,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J18" s="3"/>
@@ -4013,7 +4080,7 @@
         <v/>
       </c>
       <c r="I19" s="3" t="str">
-        <f>IF($G19="","",IFERROR(VLOOKUP($G19,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J19" s="3"/>
@@ -4043,7 +4110,7 @@
         <v/>
       </c>
       <c r="I20" s="3" t="str">
-        <f>IF($G20="","",IFERROR(VLOOKUP($G20,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J20" s="3"/>
@@ -4073,7 +4140,7 @@
         <v/>
       </c>
       <c r="I21" s="3" t="str">
-        <f>IF($G21="","",IFERROR(VLOOKUP($G21,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J21" s="3"/>
@@ -4103,7 +4170,7 @@
         <v/>
       </c>
       <c r="I22" s="3" t="str">
-        <f>IF($G22="","",IFERROR(VLOOKUP($G22,$AB$8:$AD$11,3,0),""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J22" s="3"/>
@@ -4129,7 +4196,7 @@
       <c r="L24" s="9"/>
       <c r="V24" s="26"/>
       <c r="W24" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.2">
@@ -4137,7 +4204,7 @@
       <c r="L25" s="9"/>
       <c r="V25" s="29"/>
       <c r="W25" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4159,74 +4226,77 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:Z17"/>
+  <dimension ref="A2:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
     <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5" customWidth="1"/>
+    <col min="9" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>246</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="I2" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="M2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="N2" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="M2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>271</v>
-      </c>
       <c r="O2" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>222</v>
+        <v>313</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>314</v>
       </c>
       <c r="Z2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -4245,14 +4315,15 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Y3" t="s">
-        <v>226</v>
-      </c>
+      <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -4271,8 +4342,12 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q4" s="3"/>
+      <c r="Z4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -4291,8 +4366,12 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q5" s="3"/>
+      <c r="Z5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -4311,8 +4390,9 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -4331,8 +4411,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -4351,8 +4432,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -4371,8 +4453,9 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -4391,8 +4474,9 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -4411,8 +4495,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -4431,36 +4516,37 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R15" s="42"/>
-      <c r="S15" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S15" s="42"/>
+      <c r="T15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R16" s="26"/>
-      <c r="S16" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="18:19" x14ac:dyDescent="0.2">
-      <c r="R17" s="29"/>
-      <c r="S17" s="9" t="s">
-        <v>104</v>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S16" s="26"/>
+      <c r="T16" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="29"/>
+      <c r="T17" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
-      <formula1>$Y$2:$Y$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$Z$2:$Z$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4480,22 +4566,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="E2" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4718,27 +4804,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4746,71 +4832,71 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F3" s="33"/>
       <c r="H3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I3" s="33"/>
       <c r="K3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4827,10 +4913,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4847,7 +4933,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -5136,27 +5222,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -5164,71 +5250,71 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5245,10 +5331,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5547,22 +5633,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>296</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>297</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5573,7 +5659,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -5595,7 +5681,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -5617,7 +5703,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -5629,7 +5715,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -5641,7 +5727,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -5661,7 +5747,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -6472,16 +6558,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:AP52"/>
+  <dimension ref="A2:AQ52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="41" width="8.5" customWidth="1"/>
+    <col min="11" max="42" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>79</v>
       </c>
@@ -6496,7 +6582,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>83</v>
       </c>
@@ -6517,7 +6603,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>89</v>
       </c>
@@ -6539,67 +6625,67 @@
         <v>93</v>
       </c>
       <c r="AK4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C5" s="1" t="s">
+      <c r="D5" t="s">
         <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AK5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" t="s">
         <v>105</v>
-      </c>
-      <c r="P6" t="s">
-        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -6625,7 +6711,7 @@
       <c r="Y9" s="54"/>
       <c r="Z9" s="54"/>
       <c r="AA9" s="53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AB9" s="54"/>
       <c r="AC9" s="54"/>
@@ -6633,7 +6719,7 @@
       <c r="AE9" s="54"/>
       <c r="AF9" s="54"/>
       <c r="AG9" s="53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AH9" s="54"/>
       <c r="AI9" s="54"/>
@@ -6644,136 +6730,140 @@
       <c r="AN9" s="54"/>
       <c r="AO9" s="54"/>
       <c r="AP9" s="54"/>
-    </row>
-    <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AQ9" s="54"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="D10" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="44" t="s">
+      <c r="F10" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="G10" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="I10" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="K10" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="L10" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="M10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="N10" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="P10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="P10" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="44" t="s">
+      <c r="R10" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="U10" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="V10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="W10" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="X10" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="X10" s="44" t="s">
+      <c r="Y10" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="Y10" s="44" t="s">
+      <c r="Z10" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="Z10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB10" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC10" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="AA10" s="46" t="s">
+      <c r="AD10" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE10" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="AB10" s="46" t="s">
-        <v>305</v>
-      </c>
-      <c r="AC10" s="47" t="s">
+      <c r="AF10" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>309</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AI10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AM10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AN10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="AP10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AO10" s="23" t="s">
+      <c r="AQ10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AP10" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -6894,10 +6984,13 @@
       <c r="AN11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AO11" s="3"/>
+      <c r="AO11" s="3">
+        <v>0.5</v>
+      </c>
       <c r="AP11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ11" s="3"/>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -7018,10 +7111,13 @@
       <c r="AN12" s="19">
         <v>0.0</v>
       </c>
-      <c r="AO12" s="19"/>
+      <c r="AO12" s="19">
+        <v>0.5</v>
+      </c>
       <c r="AP12" s="19"/>
-    </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ12" s="19"/>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -7066,8 +7162,9 @@
       <c r="AN13" s="19"/>
       <c r="AO13" s="19"/>
       <c r="AP13" s="19"/>
-    </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ13" s="19"/>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -7112,8 +7209,9 @@
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ14" s="3"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -7158,8 +7256,9 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ15" s="3"/>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -7204,8 +7303,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
-    </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ16" s="3"/>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -7250,8 +7350,9 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-    </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ17" s="3"/>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -7296,8 +7397,9 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
-    </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ18" s="3"/>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -7342,8 +7444,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ19" s="3"/>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -7388,8 +7491,9 @@
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ20" s="3"/>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -7434,8 +7538,9 @@
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ21" s="3"/>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -7480,8 +7585,9 @@
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ22" s="3"/>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -7526,8 +7632,9 @@
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ23" s="3"/>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -7572,8 +7679,9 @@
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ24" s="3"/>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -7618,8 +7726,9 @@
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ25" s="3"/>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -7652,8 +7761,9 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ26" s="1"/>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -7677,7 +7787,7 @@
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -7701,7 +7811,7 @@
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -7725,7 +7835,7 @@
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -7749,7 +7859,7 @@
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -7773,7 +7883,7 @@
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -8279,7 +8389,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="AG9:AP9"/>
+    <mergeCell ref="AG9:AQ9"/>
     <mergeCell ref="AA9:AF9"/>
     <mergeCell ref="C9:Z9"/>
   </mergeCells>
@@ -8359,7 +8469,7 @@
       <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM11:AN52">
+  <conditionalFormatting sqref="AM11:AO52">
     <cfRule type="expression" dxfId="18" priority="1">
       <formula>$AJ11="lf"</formula>
     </cfRule>
@@ -8407,16 +8517,16 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B2" s="3">
         <v>-10.0</v>
       </c>
       <c r="D2" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="N2" s="24" t="s">
         <v>147</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -8433,161 +8543,161 @@
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -8680,172 +8790,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -9741,277 +9851,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="D5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="G5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="H5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="J5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="K5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="M5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="N5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="P5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Q5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="T5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="T5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="W5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="W5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Z5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="AC5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="AE5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AF5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AF5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AI5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AL5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AO5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AO5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AR5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AR5" s="39" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -10104,172 +10214,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -11074,15 +11184,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="M7:N7"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="P4:Q4"/>
@@ -11091,6 +11192,13 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="S4:T4"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH4:AI4"/>
@@ -11104,6 +11212,8 @@
     <mergeCell ref="AN7:AO7"/>
     <mergeCell ref="AH7:AI7"/>
     <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="V7:W7"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11200,20 +11310,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -11221,7 +11331,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -11232,19 +11342,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -11257,7 +11367,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -11266,10 +11376,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" t="s">
         <v>192</v>
-      </c>
-      <c r="H6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11406,31 +11516,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -11458,10 +11568,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -11486,10 +11596,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -11504,10 +11614,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" t="s">
         <v>206</v>
-      </c>
-      <c r="K5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -11534,7 +11644,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -11549,7 +11659,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K8"/>
     </row>
@@ -11565,7 +11675,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9"/>
     </row>
@@ -11581,7 +11691,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K10"/>
     </row>
@@ -11597,7 +11707,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K11"/>
     </row>
@@ -11613,31 +11723,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -11646,7 +11756,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K17"/>
     </row>
@@ -11687,16 +11797,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -11707,10 +11817,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" t="s">
         <v>222</v>
-      </c>
-      <c r="F3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -11718,10 +11828,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" t="s">
         <v>224</v>
-      </c>
-      <c r="F4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -11729,10 +11839,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" t="s">
         <v>226</v>
-      </c>
-      <c r="F5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11856,128 +11966,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12417,128 +12527,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
